--- a/Ministry_of_Telecommunications_TRA.xlsx
+++ b/Ministry_of_Telecommunications_TRA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3662,6 +3662,613 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>The TRA Brings Stakeholders Together to Discuss FTTH Policy, Deployment Guidelines and Spectrum Refarming</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3919</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; The TRA Brings Stakeholders Together to Discuss FTTH Policy, Deployment Guidelines and Spectrum Refarming
+The TRA Brings Stakeholders Together to Discuss FTTH Policy, Deployment Guidelines and Spectrum Refarming
+			October 10, 2026
+On Thursday, October 1, 2026, the TRA held a workshop at the Crowne Plaza Hotel in Beirut, bringing together stakeholders to discuss FTTH policy, deployment guidelines and spectrum refarming under the theme “Shaping the Future of Lebanon’s Digital Infrastructure.” 
+Dr. Hayssam Serhan, Board Member, Head of the Information and Consumer Affairs Unit and Master of Ceremonies, opened the workshop by outlining its purpose: to build on stakeholders’ contributions to the three public consultations and to develop practical remarks through collaborative discussion. He reaffirmed the TRA’s commitment to private-sector participation and to preserving market competition, and invited participants to share their expertise and work together on solutions.
+Dr. Serhan then presented the three consultations under discussion and announced that three further consultations will be released soon, along with class licenses for data centers and cybersecurity. After introducing each speaker, he invited attendees to join the roundtable on the topic of greatest interest to them and to work toward constructive outcomes. 
+In her opening speech, TRA Chairwoman Dr. Jenny Gemayel stressed on the importance of moving from public consultation to constructive dialogue in practical ways to advance Lebanon’s telecommunications sector. She underlined the need to consider the perspectives of the public sector, operators, investors, service providers and consumers when developing a balanced and workable regulatory framework. Dr. Gemayel encouraged participants to identify areas of agreement, discuss outstanding concerns and propose practical solutions that support investment, safeguard competition, protect consumer rights and ensure the sector’s sustainability. 
+Dr. Diana Bou Ghanem, Board Member and Head of Market and Competition Unit, presented the preliminary findings of 15 stakeholder submissions to the TRA’s public consultation on FTTH policy. She highlighted broad support for long-term regulatory certainty, open access and measures to extend coverage beyond urban areas, while noting differing views on licensing models, investment protection and the use of public infrastructure. Key issues included transparent wholesale pricing, rights-of-way procedures, the financial viability of fiber deployment and the transition from unregulated networks to licensed services. These findings will enable the TRA to work on a framework that balances competition, investment and wider access to reliable connectivity. 
+Dr. Rajaa Charif, Board Member and Head of the Legal and Licensing Unit, outlined the legal framework, the TRA’s prerogatives and the implementation mechanisms under Telecommunications Law 431/2002 and the licensing regulations, emphasizing fairness, equity, transparency, competition and stakeholder participation. She also presented a development plan to standardize data, terminology, procedures and forms; update the legal and regulatory framework; establish periodic reviews of the licensing system; and ensure sound regulation that reflects the nature and risks of each service while maintaining flexibility. Dr. Charif then led an open roundtable where she addressed the legal and licensing aspects of both FTTH and spectrum throughout the day. 
+Eng. Mohamad Ayoub, Board Member and Head of the Telecommunications Technologies Unit, presented the spectrum refarming and broadband context, along with the consolidated findings of the TRA’s public consultation. He outlined stakeholder positions on reorganizing the 2.3, 2.6, 3.5 and 26 GHz bands for fixed wireless access, as well as the TRA’s proposals on market structure, spectrum assignment, migration and license obligations. He emphasized the importance of operators submitting concrete proposals on spectrum, mergers and acquisitions, and incentives to inform the TRA’s approach. 
+Following the presentations, stakeholders joined roundtable discussions. Each roundtable presented its main findings at the end of its session, allowing participants to share conclusions and contribute to the broader discussion. 
+The morning session focused on the FTTH Regulatory fFamework, market structure and deployment guidelines. The FTTH Regulatory Framework roundtable proposed an immediate transition under the existing regulatory regime to allow continued fiber deployment, alongside a review of capacity reservation and allocation arrangements, wholesale access provisions, and the separation of Ogero’s retail and wholesale activities. 
+The FTTH Market Structure roundtable called for a review of barriers to private-sector participation, the establishment of requirements that promote competition, the encouragement of joint ventures between the incumbent and other market players, and a revisit of the revenue-sharing model. 
+The FTTH Deployment Guidelines roundtable suggested to facilitate building access and customer connections, ensuring fair infrastructure sharing, improving coordination and technical standards, and adopting a phased migration and coverage roadmap that preserves service continuity and encourages rural deployment. 
+The afternoon session addressed spectrum refarming, including spectrum allocation for fixed wireless access and the regulatory framework. Initially planned as two roundtables covering separate themes, the session became a single joint discussion after attendees agreed to bring both groups together, given the importance of the topics. 
+Overall, the discussions emphasized on the need for a balanced regulatory framework that promotes fair competition, financial sustainability, efficient spectrum utilization, infrastructure investment and the long-term development of Lebanon’s telecommunications sector.
+To view the agenda, click here
+To access Dr. Diana Bou Ghanem’s presentation click here
+To view the picture gallery, click here</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:01.096654+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TRA Expert Takes Part in EMF Exposure Panel at Beirut Arab University in Tripoli</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3925</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; TRA Expert Takes Part in EMF Exposure Panel at Beirut Arab University in Tripoli
+TRA Expert Takes Part in EMF Exposure Panel at Beirut Arab University in Tripoli
+			October 09, 2026
+On 9 October 2026, the TRA took part in a panel discussion on electromagnetic field (EMF) exposure at Beirut Arab University in Tripoli. 
+Representing the TRA, Eng. Sahar Cheaito, Spectrum Management Expert, presented international EMF exposure guidelines and recent scientific developments. She highlighted the Authority’s regulatory role in setting exposure limits and monitoring compliance. She also addressed EMF considerations related to 5G and other emerging technologies, as well as ongoing efforts to update Lebanon’s EMF regulatory framework. 
+The discussions provided valuable insights to support the ongoing revision of the EMF regulation.
+To view the presentation, click here</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:07.424260+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>The TRA Extends the Submission Deadline for the Consultancy Services RFP</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3916</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; The TRA Extends the Submission Deadline for the Consultancy Services RFP
+The TRA Extends the Submission Deadline for the Consultancy Services RFP
+			October 07, 2026
+The TRA has extended the submission deadline for its Request for Proposals (RFP) for Consultancy Services from 13 October 2026 to 23 October 2026 at 12:00 PM, following requests from several interested and potential bidders. 
+The RFP seeks to engage a specialized consulting firm to assist in and validate the preparation of tender documents, two Management and Operating Agreements (MOAs), and financial models for MIC1 (Alfa) and MIC2 (Touch), as well as participation requirements and pre-qualification criteria for the international tender.
+The extension provides interested bidders with additional time to prepare and submit comprehensive proposals. 
+Click here to access the initial RFP announcement
+Click here to access the procurement notice and tender documents published on the electronic platform of the Public Procurement Authority (PPA). 
+Click on the links to access the Invitation Letter in English and Arabic.
+Click on the links to access the RFP document in English and Arabic.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:09.462347+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TRA Chairwoman Moderates Panel on Lebanon’s Digital Infrastructure at Project Lebanon 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3922</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>October 05, 2026
+As part of 
+Project Lebanon 2026
+, 
+Dr. Jenny Gemayel, Chairwoman of the Telecommunications Regulatory Authority
+, moderated a panel dedicated to the rebuilding and modernization of Lebanon’s digital infrastructure. 
+The session brought together different public, private, financial and international perspectives, leading to a rich and constructive discussion on fiber, mobile networks, 5G, investment, infrastructure sharing and the regulatory conditions needed to support Lebanon’s digital future. 
+The discussion was particularly valuable in highlighting the different views, priorities and challenges facing the sector. Topics included the national backbone, fiber and FTTH deployment, mobile network modernization, 5G readiness, international connectivity, infrastructure sharing, taxation, financing and the respective roles of public and private actors. 
+Dr. Gemayel highlighted the TRA’s role in creating a regulatory framework that supports competition, enables investment, promotes the efficient use of spectrum and contributes to a more structured and sustainable telecommunications market. She also referred to the TRA’s ongoing work on spectrum policy and its consultation on fiber and FTTH deployment. 
+The panel also explored regional and international experience, as well as the growing infrastructure requirements associated with cloud services, AI, IoT and increasing data demand. 
+The exchange showed that there is no single solution to Lebanon’s digital infrastructure challenges. Progress will depend on bringing together different perspectives, aligning the roles of the various stakeholders and translating discussion into coordinated implementation.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:15.874645+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>The TRA will Hold a Workshop on FTTH Policy, Deployment Guidelines and Spectrum Refarming</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3908</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; The TRA will Hold a Workshop on FTTH Policy, Deployment Guidelines and Spectrum Refarming
+The TRA will Hold a Workshop on FTTH Policy, Deployment Guidelines and Spectrum Refarming
+			September 28, 2026
+The TRA will hold a workshop on Thursday, 1 October 2026, at Crowne Plaza Beirut, bringing together stakeholders to discuss its three recent consultations on the FTTH Access Network Licensing Policy, Optical Fiber Deployment Guidelines, and spectrum refarming. 
+The agenda will include roundtable discussions on the topics covered by the consultations. These sessions will give stakeholders an opportunity to express their views, share practical insights, and discuss their recommendations directly with the TRA. 
+Public consultation and listening to stakeholders are central to the TRA’s work. By bringing different perspectives into the discussion, the Authority aims to develop sound policies and lay stronger foundations for Lebanon’s telecommunications sector. 
+To view the agenda of the workshop click here</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:22.178956+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TRA Updates FAQs on Starlink Satellite Internet Services in Lebanon</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3900</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; TRA Updates FAQs on Starlink Satellite Internet Services in Lebanon
+TRA Updates FAQs on Starlink Satellite Internet Services in Lebanon
+			September 23, 2026
+Click on the link below:
+FAQs – Starlink Satellite Internet Services in Lebanon</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:28.595543+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TRA Launches the Process to Regularize Internet Subscriptions</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3902</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; TRA Launches the Process to Regularize Internet Subscriptions
+TRA Launches the Process to Regularize Internet Subscriptions
+			September 23, 2026
+Pursuant to Telecommunications Regulatory Authority (TRA) Decision No. 4/2026, issued on 5 February 2026, the TRA has launched the process of regularizing Internet subscriptions and transitioning subscribers from unlicensed to licensed networks. 
+Oversight of the process is being carried out in close coordination with licensed Internet Service Providers (ISPs) and the relevant judicial and security authorities, in order to ensure an orderly and smooth transition. 
+All users connected through unlicensed networks in the areas served by the following ten Ogero central offices are called upon to begin the transition without delay: Ashrafieh, Hamra, Badaro, Adlieh, Mina El Hosn, Ras Beirut, Baabda, Hazmieh, Tripoli – El Mina and Tripoli – El Bahsas. 
+A licensed ISP may make contact to arrange the regularization of a subscription. In that case, subscribers cooperate with the provider and submit the information and documents required to complete the transition. 
+Anyone who is not contacted should ask their current provider for the name of the licensed ISP serving their area. It is also possible to consult the list of licensed ISPs and approach a provider directly to begin the required procedures. 
+Completing the transition as soon as possible is strongly recommended, in order to avoid any interruption to Internet service. 
+To learn more about the regularization process and the steps to follow, watch the TRA's awareness video.
+For further information or assistance, contact the TRA at info@tra.gov.lb.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:34.902841+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>The TRA Clarifies Procedures for Devices Subject to Unsettled Customs Fees</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3872</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>August 20, 2026
+The TRA has recently received a number of queries and complaints from consumers and companies concerning devices suspended from Lebanese mobile networks, or for which notifications have been received regarding unsettled customs fees. These devices had been operating on Lebanese mobile networks without a recorded customs payment associated with their 
+IMEI
+ number. 
+Concerned device owners are being notified by SMS from the Ministry of Finance and are asked to regularize their device's status within the deadline stated in the notification. Failing to do so will result in the device's suspension from mobile networks. 
+These amounts represent customs duties and are neither imposed nor collected by the TRA. The TRA's role is limited to facilitating the regularization and reactivation process where its intervention is required. 
+Accordingly, the TRA is issuing the following clarification to assist subscribers who have received an SMS indicating that customs fees related to their mobile device have not yet been recorded as settled. 
+What to do based on your situation? 
+- I received the SMS and want to pay 
+- I already paid the customs fees, but I still received the notification to pay by SMS
+- I am a commercial company using modems, routers, switches and GPS with IMEI numbers
+- I am a commercial company using modems, routers, switches and GPS with IMEI numbers that have not been pre-authorized/verified
+The TRA remains committed to assisting concerned consumers and ensuring clear coordination among the relevant public authorities and service providers. 
+For further assistance, consumers may contact the TRA at 
+info@tra.gov.lb
+.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:41.394178+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>The TRA is launching an RFP for consulting services</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3906</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; The TRA is launching an RFP for consulting services
+The TRA is launching an RFP for consulting services
+			September 23, 2026
+The TRA is launching a procurement process through a Request for Proposal (RFP) for consulting services to engage a specialized consulting firm to assist in and validate the preparation of the tender documents, the two Management and Operating Agreements (MOAs), and the financial models for MIC1 (Alfa) and MIC2 (Touch), as well as the participation requirements and prequalification criteria for the international tender. 
+This process is based on the Council of Ministers Decision No. 5 of 15 January 2026 and Decision No. 10 dated 10 September 2026. 
+The assignment primarily covers the review and structuring of the technical, operational, financial, commercial, legal, and contractual aspects of the future arrangements; the development of a performance indicators framework and risk allocation structure. It also includes the preparation of integrated and auditable financial models, the tender documents, and the two Management and Operating Agreements. 
+These deliverables are intended to enable the launch of a competitive process for the selection of the entities that will manage and operate the two mobile networks, with the selected entities assuming responsibility for operating expenditures (OPEX) and capital expenditures (CAPEX). 
+The assignment also includes, on an optional basis and if activated by the TRA, the provision of advisory support during the tendering and related procurement procedures. 
+The assignment will be carried out in accordance with the applicable Lebanese legal and regulatory frameworks, in particular Telecommunications Law No. 431/2002, Public Procurement Law No. 244/2021, the relevant Council of Ministers decisions, and the applicable regulatory decisions and regulations. 
+Click here to access the procurement notice and tender documents published on the electronic platform of the Public Procurement Authority (PPA). 
+Click on the links to access the Invitation Letter in English and Arabic.
+Click on the links to access the RFP document in English and Arabic.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:43.397060+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TRA Extends Deadlines for Two Major Consultations</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3886</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>September 08, 2026
+The TRA has extended the deadline for submitting comments and feedback on the following consultation documents: 
+- "Optical Fiber Deployment Guidelines"
+- "FTTH Access Network Licensing and Deployment Policy"
+The new deadline to submit feedback for both consultations is 
+5:00 p.m. local time on Monday, September 21, 2026. The TRA appreciates stakeholders' continued engagement and valuable contributions to this consultation, and encourages those who have not yet submitted their comments to make use of the additional time to review the draft Guidelines and actively contribute to the process. 
+Comments and feedback should be submitted separately for each consultation as follows: 
+Draft "Optical Fiber Deployment Guidelines" 
+Draft "FTTH Access Network Licensing and Deployment Policy"</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:49.801423+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Children Online Protection at the Core of Its Mission: the TRA Publishes a Dedicated Newsletter</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3882</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; Children Online Protection at the Core of Its Mission: the TRA Publishes a Dedicated Newsletter
+Children Online Protection at the Core of Its Mission: the TRA Publishes a Dedicated Newsletter
+			August 31, 2026
+The TRA announces the publication of its August 2026 newsletter on Children Online Protection, titled "Protecting Children in the Digital World: From Global Experience to the TRA's Vision for a National Framework in Lebanon." 
+The newsletter examines the risks children face in online environments, reviews international approaches to child online safety, and highlights the TRA's own experience and initiatives in this field. It also outlines the TRA's vision for a coordinated national framework in Lebanon, alongside practical guidance to support parents and caregivers in protecting children online. 
+Read the full newsletter to learn more about the TRA's ongoing commitment to children online protection:
+Protecting Children in the Digital World: From Global Experience to the TRA's Vision for a National Framework in Lebanon</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:41:56.093828+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>The TRA Cancels the Public Procurement for Consultancy Services to Support the Preparation of the Mobile Networks Management and Operating Agreement Tender</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3862</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; The TRA Cancels the Public Procurement for Consultancy Services to Support the Preparation of the Mobile Networks Management and Operating Agreement Tender
+The TRA Cancels the Public Procurement for Consultancy Services to Support the Preparation of the Mobile Networks Management and Operating Agreement Tender
+			August 13, 2026
+The TRA announces the cancellation of the Procurement related to the Request for Proposal for Consultancy Services to Support the Preparation of the Mobile Networks Management and Operating Agreement (MOA) Tender. The process was launched on 5 March 2026 and published on the Public Procurement Authority’s electronic platform under reference 11337. 
+The Request for Proposal sought to engage a qualified international consultancy firm to support the preparation of a competitive tender process for the management and operation of Lebanon’s two state-owned mobile networks, MIC1 (Alfa) and MIC2 (Touch). 
+Pursuant to the mandate granted to the TRA by the Council of Ministers, the consultancy assignment was intended to support the preparation of a modern Management and Operating Agreement framework. Its scope included the development of the complete tender package and MOAs, and the preparation of a robust financial model of the two mobile businesses Alfa and Touch. 
+Following the submission and evaluation of proposals, the TRA Board issued Decision No. 10/2026, cancelling the procurement, prior to notification and contract award, due to insufficient budgetary appropriations. The cancellation was made in accordance with Article 25 of Public Procurement Law No. 244/2021. 
+All participating bidders were formally notified of the cancellation. The TRA will return the bid bonds and, where applicable, any other relevant documents submitted as part of the proposals. Bidders are requested to visit the TRA’s premises to collect their returned items. 
+The TRA thanks all participating bidders for the time and effort invested in preparing and submitting their valuable proposals. 
+To view Decision No. 10/2026, click here
+To view the Cancellation notice on the Public Procurement Authority’s electronic platform, click here</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:42:02.409118+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>The TRA launches the "FTTH Access Network Licensing and Deployment Policy" draft document for public consultation</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3858</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>August 12, 2026
+The draft consultation on 
+"FTTH Access Network Licensing and Deployment Policy"
+ is designed to provide stakeholders and industry players in the telecommunications sector with the TRA’s proposed policy and views regarding the deployment of Fiber-to-the-Home (FTTH) networks. This consultation forms part of the TRA’s ongoing efforts to support the modernization and development of Lebanon’s telecommunications sector. 
+This document proposes a framework for the staged and widespread rollout of fiber access infrastructure across Lebanon and aims to modernize broadband infrastructure, support the legalization of existing broadband activities, attract sustainable private investment, and facilitate the deployment of next-generation broadband services and digital platforms. 
+Through this consultation, stakeholders and industry players are invited to submit their comments and feedback on the proposed policy framework and deployment approach. 
+The feedback received will support the issuance of TRA policies and directives concerning the rollout of FTTH networks and contribute to improving connectivity services for citizens and businesses, while supporting Lebanon’s transition toward a competitive and digitally enabled economy. 
+The "FTTH Access Network Licensing and Deployment Policy" draft document is now being launched for consultation. Interested parties are requested to submit their feedback no later than 
+5:00 p.m. local time
+ on 
+Wednesday, September 9, 2026
+ to 
+FTTHnetworkrollout@tra.gov.lb
+, after having reviewed the following documents:</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:42:08.701280+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>The TRA launches the "Optical Fiber Deployment Guidelines" draft document for public consultation</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3860</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>August 12, 2026
+The consultation on the 
+draft "Optical Fiber Deployment Guidelines"
+ aims to establish a practical national framework for the safe, efficient, and standardized deployment of high-quality fiber-optic infrastructure in Lebanon, aligned with applicable legislation, international standards, and recognized industry best practices. 
+The proposed Guidelines seek to improve coordination and interoperability among relevant stakeholders, enhance the quality and consistency of fiber deployments, reduce unnecessary civil works, facilitate broadband expansion, and support the long-term development of Lebanon’s telecommunications infrastructure. 
+The 
+draft "Optical Fiber Deployment Guidelines" are now being launched for consultation. Interested parties are requested to review the following documents and submit their feedback by 
+5:00 p.m. local time on Wednesday, September 9, 2026
+: 
+Responses to the consultation should be submitted in PDF or Microsoft Word format, together with the completed consultation cover sheet, to 
+fiber_guidelines@tra.gov.lb
+ by the consultation deadline.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:42:14.997623+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>The TRA Calls for an Action-Oriented National Strategy to Protect Children Online</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3856</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>July 23, 2026
+The TRA participated in the first meeting of the 
+Ministerial Committee on the National Plan for Children’s Safe Internet Use
+ tasked with preparing a comprehensive national strategy and vision to promote the safe and responsible use of the internet and digital applications by children. 
+Held at the 
+Ministry of Information premises on Thursday 23rd July, the meeting brought together representatives from the Ministry of Information, the TRA, the Ministry of Social Affairs through the Higher Council for Childhood, the Ministry of Education, the Internal Security Forces, Ogero, SMEX, the René Moawad Foundation, MITAI, and other organizations and stakeholders active in child online protection. 
+At the opening of the meeting, the NGO 
+SMEX
+ presented a unified strategic vision for developing the national plan. The presentation emphasized the need for a coordinated, multi-stakeholder approach bringing together public institutions, civil society organizations, technical experts, and relevant service providers. 
+Participating institutions presented the initiatives and measures they have implemented in the areas of child online protection and digital safety. Discussions also addressed opportunities for future cooperation, the distribution of institutional responsibilities, and the establishment of effective implementation, monitoring, and follow-up mechanisms. 
+Representing the TRA, 
+Dr. Rajaa Charif Board Member, and Head of Licensing and Legal Affairs Unit
+, called for the adoption of a practical, result-oriented approach supported by clear responsibilities and measurable objectives. She proposed forming a smaller steering committee to establish specialized task forces covering the different areas of child online protection, while overseeing implementation, coordination, monitoring, and follow-up. She also recommended setting a clear deadline for launching the national strategy. She stated: 
+“Protecting children online requires more than a general vision. It requires clear responsibilities, specialized task forces, measurable results, and a defined timeline that transforms national cooperation into concrete action” Also representing the TRA, on behalf of 
+Board Member and Head of the Information and Consumer Affairs Unit Dr. Hayssam Serhan, Ms. Corine Feghaly, Consumer Affairs and Public Consultation Manager
+ responsible for child online protection at the TRA, presented the Authority’s work in this field, particularly the 
+e-Aman online platform
+, which provides guidance and educational resources for children, parents, and teachers. She also highlighted the TRA’s cooperation with Lebanese ministries, civil society organizations, the International Telecommunication Union, and other international partners. 
+The TRA confirmed its readiness to share its expertise, resources, and practical experience with the members of the committee and to contribute actively to the preparation and implementation of the national strategy. 
+H.E. Paul Morcos, Minister of Information
+, thanked the participating institutions for their contributions and reaffirmed the importance of sustained cooperation among public authorities, technical bodies, civil society organizations, and other stakeholders to develop a comprehensive and effective national framework for protecting children in the digital environment.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:42:21.384477+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>The TRA Announces Further Extension of Spectrum Re-farming Consultation Deadline</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.tra.gov.lb/NewsDetails.aspx?pageid=3848</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[  Print ]   T | T
+News &gt; The TRA Announces Further Extension of Spectrum Re-farming Consultation Deadline
+The TRA Announces Further Extension of Spectrum Re-farming Consultation Deadline
+			July 21, 2026
+The TRA has further extended the deadline for submitting responses to the public consultation on “Spectrum Re-farming: Broadband Context and Framework.” Stakeholders may now provide their comments and feedback until 28 August 2026.
+The additional period is intended to allow interested parties sufficient time to examine the consultation document, assess the proposed framework, and prepare comprehensive and well-supported responses.
+Through this consultation, the TRA is seeking stakeholder views on the reorganization of spectrum use, with the objective of promoting more efficient spectrum management, improving broadband services, and supporting the introduction of future technologies.
+The TRA invites all concerned stakeholders to participate actively in the consultation process. Their technical expertise, market knowledge, and practical feedback will play an important role in ensuring effective market organization and in developing a regulatory framework that responds to the sector’s current needs and future challenges. 
+Responses may be submitted by email to spectrum_refarming@tra.gov.lb or delivered by courier to the TRA premises, Ministry of Telecommunications Building, Beirut Down Town. 
+To view the consultation document click here</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:42:27.700523+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Telecommunications_TRA.xlsx
+++ b/Ministry_of_Telecommunications_TRA.xlsx
@@ -414,7 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
